--- a/CDF_Heating_Element_Cost/SplineCDF_Fall2025_Heat Elem Cost.xlsx
+++ b/CDF_Heating_Element_Cost/SplineCDF_Fall2025_Heat Elem Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Heating_Element_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51CE737-78E0-4798-8450-C016AAA069E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{F51CE737-78E0-4798-8450-C016AAA069E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{804F8D14-DFA4-4D06-B5D9-64D51DF83B8B}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6566,127 +6566,127 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>1</v>
+        <v>0.54833587137027595</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>1.05</v>
+        <v>0.74862420436354782</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.95</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>0</v>
+        <v>7.6876876876876721E-2</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>-1.1102230246251565E-16</v>
+        <v>-0.12132132132132106</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>0.15000000000000013</v>
+        <v>0.19444444444444436</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-0.15000000000000002</v>
+        <v>-0.14833587137027593</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>0.99999999999999922</v>
-      </c>
-      <c r="K2">
+        <v>0.76287019561856229</v>
+      </c>
+      <c r="K2" t="e">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>1</v>
-      </c>
-      <c r="L2">
+        <v>#NUM!</v>
+      </c>
+      <c r="L2" t="e">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>1</v>
-      </c>
-      <c r="M2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N2" t="e">
+        <v>1.699137369791671</v>
+      </c>
+      <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O2" t="e">
+        <v>-0.89014198466818872</v>
+      </c>
+      <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>#DIV/0!</v>
+        <v>0.3797742915698239</v>
       </c>
       <c r="P2" t="e">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="Q2" t="e">
         <f ca="1">P2^(1/3)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="R2" t="e">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="S2" t="e">
         <f ca="1">-Q2</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="T2" t="e">
         <f ca="1">COS(R2/3)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="U2" t="e">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>#DIV/0!</v>
+        <v>0.52604166666666663</v>
       </c>
       <c r="W2" t="e">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="X2" t="e">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="Y2" t="e">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z2">
         <f ca="1">-N2/2+SQRT(O2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>1.0613292917263411</v>
+      </c>
+      <c r="AA2">
         <f ca="1">Z2^(1/3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB2" t="e">
+        <v>1.0200388591264851</v>
+      </c>
+      <c r="AB2">
         <f ca="1">-N2/2-SQRT(O2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC2" t="e">
+        <v>-0.17118730705815227</v>
+      </c>
+      <c r="AC2">
         <f ca="1">AB2^(1/3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD2" t="e">
+        <v>-0.55525249670283316</v>
+      </c>
+      <c r="AD2">
         <f ca="1">AA2+AC2+V2</f>
-        <v>#DIV/0!</v>
+        <v>0.99082802909031853</v>
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>1</v>
+        <v>0.99082802909031853</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36520,15 +36520,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000B92449D07C8D4B9A11B36D3DD1493B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12876fd8bd5d90ce750491db8e9e67c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18b8549e-3e0d-4ec5-af2b-e3bc54260487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45151d2993f903c2059e1e395416a0b1" ns2:_="">
     <xsd:import namespace="18b8549e-3e0d-4ec5-af2b-e3bc54260487"/>
@@ -36666,6 +36657,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -36673,14 +36673,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172819F6-475E-4EC6-B459-4AE9BCA56E70}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{219EC5AA-EECD-41BC-AC7B-18D37A1D1A5B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36698,6 +36690,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172819F6-475E-4EC6-B459-4AE9BCA56E70}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32954AA9-D9DB-498C-8567-283EF2F8DB2B}">
   <ds:schemaRefs>

--- a/CDF_Heating_Element_Cost/SplineCDF_Fall2025_Heat Elem Cost.xlsx
+++ b/CDF_Heating_Element_Cost/SplineCDF_Fall2025_Heat Elem Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Heating_Element_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{F51CE737-78E0-4798-8450-C016AAA069E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{804F8D14-DFA4-4D06-B5D9-64D51DF83B8B}"/>
+  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{F51CE737-78E0-4798-8450-C016AAA069E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BE9112B-4624-4450-9F10-991100AEAC9F}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4804,6 +4804,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6566,127 +6570,127 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>0.54833587137027595</v>
+        <v>0.80757287203040196</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>0.74862420436354782</v>
+        <v>0.92499999999999993</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.60000000000000009</v>
+        <v>0.85</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>7.6876876876876721E-2</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>-0.12132132132132106</v>
+        <v>5.5511151231257827E-17</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>0.19444444444444436</v>
+        <v>0.14999999999999997</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-0.14833587137027593</v>
+        <v>-0.107572872030402</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>0.76287019561856229</v>
-      </c>
-      <c r="K2" t="e">
+        <v>0.71715248020268019</v>
+      </c>
+      <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L2" t="e">
+        <v>0.75</v>
+      </c>
+      <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="M2">
+        <v>0.75</v>
+      </c>
+      <c r="M2" t="e">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>1.699137369791671</v>
-      </c>
-      <c r="N2">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N2" t="e">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>-0.89014198466818872</v>
-      </c>
-      <c r="O2">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O2" t="e">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>0.3797742915698239</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P2" t="e">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>#NUM!</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q2" t="e">
         <f ca="1">P2^(1/3)</f>
-        <v>#NUM!</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R2" t="e">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>#NUM!</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S2" t="e">
         <f ca="1">-Q2</f>
-        <v>#NUM!</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="T2" t="e">
         <f ca="1">COS(R2/3)</f>
-        <v>#NUM!</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="U2" t="e">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="V2">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V2" t="e">
         <f ca="1">-G2/F2/3</f>
-        <v>0.52604166666666663</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="W2" t="e">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>#NUM!</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X2" t="e">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>#NUM!</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Y2" t="e">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z2">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z2" t="e">
         <f ca="1">-N2/2+SQRT(O2)</f>
-        <v>1.0613292917263411</v>
-      </c>
-      <c r="AA2">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA2" t="e">
         <f ca="1">Z2^(1/3)</f>
-        <v>1.0200388591264851</v>
-      </c>
-      <c r="AB2">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB2" t="e">
         <f ca="1">-N2/2-SQRT(O2)</f>
-        <v>-0.17118730705815227</v>
-      </c>
-      <c r="AC2">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC2" t="e">
         <f ca="1">AB2^(1/3)</f>
-        <v>-0.55525249670283316</v>
-      </c>
-      <c r="AD2">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD2" t="e">
         <f ca="1">AA2+AC2+V2</f>
-        <v>0.99082802909031853</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>0.99082802909031853</v>
+        <v>0.75</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36520,6 +36524,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000B92449D07C8D4B9A11B36D3DD1493B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12876fd8bd5d90ce750491db8e9e67c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18b8549e-3e0d-4ec5-af2b-e3bc54260487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45151d2993f903c2059e1e395416a0b1" ns2:_="">
     <xsd:import namespace="18b8549e-3e0d-4ec5-af2b-e3bc54260487"/>
@@ -36657,15 +36670,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -36673,6 +36677,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172819F6-475E-4EC6-B459-4AE9BCA56E70}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{219EC5AA-EECD-41BC-AC7B-18D37A1D1A5B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36690,14 +36702,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172819F6-475E-4EC6-B459-4AE9BCA56E70}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32954AA9-D9DB-498C-8567-283EF2F8DB2B}">
   <ds:schemaRefs>

--- a/CDF_Heating_Element_Cost/SplineCDF_Fall2025_Heat Elem Cost.xlsx
+++ b/CDF_Heating_Element_Cost/SplineCDF_Fall2025_Heat Elem Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Heating_Element_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{F51CE737-78E0-4798-8450-C016AAA069E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BE9112B-4624-4450-9F10-991100AEAC9F}"/>
+  <xr:revisionPtr revIDLastSave="1354" documentId="13_ncr:1_{F51CE737-78E0-4798-8450-C016AAA069E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E113836D-B221-42F0-9CD2-249BFE029E45}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6570,127 +6570,127 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>0.80757287203040196</v>
+        <v>0.38331537191513998</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>0.92499999999999993</v>
+        <v>0.58890859637213855</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.85</v>
+        <v>0.54</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.95</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>0</v>
+        <v>-5.5555555555555525E-2</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>5.5511151231257827E-17</v>
+        <v>8.8888888888888892E-2</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>0.14999999999999997</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-0.107572872030402</v>
+        <v>-8.3315371915139991E-2</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>0.71715248020268019</v>
+        <v>1.2497305787270998</v>
       </c>
       <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>0.75</v>
+        <v>0.66323067477575759</v>
       </c>
       <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>0.75</v>
-      </c>
-      <c r="M2" t="e">
+        <v>0.66323067477575759</v>
+      </c>
+      <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N2" t="e">
+        <v>-2.053333333333335</v>
+      </c>
+      <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O2" t="e">
+        <v>0.55626928706511181</v>
+      </c>
+      <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P2" t="e">
+        <v>-0.24327883748814361</v>
+      </c>
+      <c r="P2">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q2" t="e">
+        <v>0.56624881229113899</v>
+      </c>
+      <c r="Q2">
         <f ca="1">P2^(1/3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R2" t="e">
+        <v>0.82731157639939079</v>
+      </c>
+      <c r="R2">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S2" t="e">
+        <v>2.0842494661090019</v>
+      </c>
+      <c r="S2">
         <f ca="1">-Q2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T2" t="e">
+        <v>-0.82731157639939079</v>
+      </c>
+      <c r="T2">
         <f ca="1">COS(R2/3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U2" t="e">
+        <v>0.76821388807975899</v>
+      </c>
+      <c r="U2">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V2" t="e">
+        <v>1.1088472692323945</v>
+      </c>
+      <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W2" t="e">
+        <v>0.53333333333333366</v>
+      </c>
+      <c r="W2">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X2" t="e">
+        <v>1.8044378188516748</v>
+      </c>
+      <c r="X2">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y2" t="e">
+        <v>-1.0195810917206489</v>
+      </c>
+      <c r="Y2">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>#DIV/0!</v>
+        <v>0.81514327286897514</v>
       </c>
       <c r="Z2" t="e">
         <f ca="1">-N2/2+SQRT(O2)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="AA2" t="e">
         <f ca="1">Z2^(1/3)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="AB2" t="e">
         <f ca="1">-N2/2-SQRT(O2)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="AC2" t="e">
         <f ca="1">AB2^(1/3)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="AD2" t="e">
         <f ca="1">AA2+AC2+V2</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>0.75</v>
+        <v>0.81514327286897514</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36524,12 +36524,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -36671,15 +36668,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172819F6-475E-4EC6-B459-4AE9BCA56E70}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32954AA9-D9DB-498C-8567-283EF2F8DB2B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -36703,10 +36704,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32954AA9-D9DB-498C-8567-283EF2F8DB2B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172819F6-475E-4EC6-B459-4AE9BCA56E70}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>